--- a/docs/Voyager-UIUX-Timesheet-Aug2026.xlsx
+++ b/docs/Voyager-UIUX-Timesheet-Aug2026.xlsx
@@ -901,7 +901,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="58" customHeight="1">
+    <row r="10" ht="44" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t>19/08/2026</t>
@@ -961,7 +961,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="58" customHeight="1">
+    <row r="13" ht="44" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
           <t>20/08/2026</t>
@@ -981,7 +981,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="58" customHeight="1">
+    <row r="14" ht="44" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
           <t>20/08/2026</t>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="58" customHeight="1">
+    <row r="15" ht="44" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
           <t>21/08/2026</t>
@@ -1021,7 +1021,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="58" customHeight="1">
+    <row r="16" ht="44" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
           <t>21/08/2026</t>
@@ -1061,7 +1061,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="58" customHeight="1">
+    <row r="18" ht="44" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
           <t>23/08/2026</t>
@@ -1101,7 +1101,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="58" customHeight="1">
+    <row r="20" ht="44" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
           <t>23/08/2026</t>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="58" customHeight="1">
+    <row r="21" ht="44" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
           <t>23/08/2026</t>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="58" customHeight="1">
+    <row r="23" ht="44" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
         <is>
           <t>23/08/2026</t>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Metadata verification. Audited every dropdown in the prototype against the system's own GET /api/MetadataType. Found most option lists were incorrect — Project Type had 1 of 4 correct values, Quote Focus 1 of 4, Material Packaging 1 of 4, and Test Requirements was modelled as free text when it is a fixed list. All replaced with the system's real enumerations.</t>
+          <t>Checked every dropdown against the system's own list of valid values. Most were wrong — for example, only 1 of the 4 Project Type options was real, and Test Requirements had been built as a free-text box when it is actually a fixed list. All corrected, so the prototype now offers only values the system will accept.</t>
         </is>
       </c>
       <c r="C24" s="6" t="n">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>Risk: would have caused rejected input</t>
+          <t>Risk: prevents rejected input</t>
         </is>
       </c>
     </row>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Requirements definition session. Produced eight recorded decisions, each with rationale and supporting evidence, and a written PRD covering functional requirements, acceptance criteria and explicit scope boundaries. Core decision: improve legibility, density and state handling without renaming screens, regrouping navigation or moving fields.</t>
+          <t>Agreed and wrote down what we are building: eight decisions with the reasoning behind each, and a requirements document setting out what 'done' means. Main decision — make the screens easier to read and use, without renaming screens, regrouping the menu or moving fields that staff already know.</t>
         </is>
       </c>
       <c r="C25" s="10" t="n">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>Deliverable: PRD</t>
+          <t>Deliverable: requirements document</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Production bundle forensics. Retrieved and analysed the shipped production JavaScript (228 modules) and decoded its obfuscated string tables to recover the true specification of features that cannot be exercised without writing records to the live system — the Run Quotation wizard, BoM Comparison, and the RFQ form's field dependencies.</t>
+          <t>Read the live system's own program code to find out how Run Quotation, BoM Comparison and the RFQ form really behave. These cannot be tested directly, because running them creates real records and costs money. This gave us the true design instead of an educated guess.</t>
         </is>
       </c>
       <c r="C26" s="6" t="n">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Fidelity restoration. Applied the requirements decisions and the recovered specifications: reverted renamed navigation and nine renamed labels, restored the live menu structure verbatim, and rebuilt Run Quotation and BoM Comparison — restoring three capabilities that had been dropped and removing an invented summary screen.</t>
+          <t>Put back everything that had drifted away from the real system: the original menu structure, nine labels that had been reworded, and the correct design of Run Quotation and BoM Comparison. Restored three features that had been left out, and removed one screen that did not exist in the real system.</t>
         </is>
       </c>
       <c r="C27" s="10" t="n">
@@ -1257,11 +1257,11 @@
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>Fidelity correction</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="58" customHeight="1">
+          <t>Correction</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="44" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
           <t>24/08/2026</t>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Defect fix: a blank page on Run Quotation step 2, traced to a CSS containment property breaking the browser compositor. Diagnosis was non-obvious — the markup, geometry and computed styles were all correct.</t>
+          <t>Fixed a blank screen on Run Quotation step 2. Difficult to trace, because the page was correct in every measurable way — it simply was not drawing. Cause was one styling rule interfering with the browser's rendering.</t>
         </is>
       </c>
       <c r="C28" s="6" t="n">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>Design review response, round 1. Implemented smart buttons for related-record navigation (previously absent entirely), grouped the record header fields into labelled regions, redesigned the priority indicator, and built the quick and advanced filter tiers plus a column chooser.</t>
+          <t>Acted on the first half of the design review. Added buttons linking an RFQ to its related records, which the screen had none of before; grouped the header fields into labelled sections so related information sits together; replaced the star rating with a clearer priority label; and built both levels of filtering plus a column picker.</t>
         </is>
       </c>
       <c r="C29" s="10" t="n">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Design review response, round 2. Global header with clock, timezone and language selector; My Queues as a header icon with badge; breadcrumb removal; per-item navigation icons for the collapsed menu; pagination at the grid foot; clickable KPI summary; row density moved to user preferences; consistent date format and label casing; activity log grouped by day and by user.</t>
+          <t>Acted on the rest of the review: clock, timezone and language in the top bar; My Queues as an icon with a count, reachable from any screen; page navigation moved to the bottom of the list; clickable summary tiles; row height moved into user settings; one consistent date format; and the activity log grouped by day and by person.</t>
         </is>
       </c>
       <c r="C30" s="6" t="n">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>Live system research session. Signed-in walkthrough capturing the true design of the Advanced Filter (no operators; explicit date From/To pairs), the View Setting dialog and its Filter, Column and Sort tabs, the record form's complete field set and section names, the real option values, and the pager format. Documented as a verified specification.</t>
+          <t>Signed in to the live system and recorded how it actually works — the filter panel, the saved-view settings and its three tabs, every field on the RFQ form, the real option values and the page numbering. Written up as a verified reference, so later work is checked against fact rather than memory.</t>
         </is>
       </c>
       <c r="C31" s="10" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>Deliverable: live specification</t>
+          <t>Deliverable: verified reference</t>
         </is>
       </c>
     </row>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Fidelity corrections from that research. Restored the live tab and section names (all five tab names and all four section names had drifted), added the (*) required markers carried by 19 fields, corrected two label casings, and removed three fields that do not exist on the live record.</t>
+          <t>Corrected what that research showed had drifted. All five tab names and all four section headings are back to the wording staff actually see, the 19 mandatory fields now carry their red (*) marker, two labels were fixed, and three fields that do not exist on the real form were removed.</t>
         </is>
       </c>
       <c r="C32" s="6" t="n">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>Fidelity correction</t>
+          <t>Correction</t>
         </is>
       </c>
     </row>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>Client answer implementation and documentation. Applied the confirmed read-only field treatment (grey only in edit mode, white boxes in view mode), parked the My Queues module at the client's request, and updated the specification and gap documents to match the agreed scope.</t>
+          <t>Applied the client's two answers: grey boxes only while editing, white boxes when simply viewing; and paused the My Queues screen at their request. Updated the specification and the outstanding-work list to match the agreed scope.</t>
         </is>
       </c>
       <c r="C33" s="10" t="n">
@@ -1394,6 +1394,7 @@
       </c>
       <c r="D34" s="12" t="n"/>
     </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" s="15" t="inlineStr">
         <is>

--- a/docs/Voyager-UIUX-Timesheet-Aug2026.xlsx
+++ b/docs/Voyager-UIUX-Timesheet-Aug2026.xlsx
@@ -769,7 +769,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1435,6 +1435,157 @@
         <is>
           <t>•  Current phase covers layout and user experience. Visual design — colour, spacing, typography and component styling — is a later phase, so that it is not done twice.</t>
         </is>
+      </c>
+    </row>
+    <row r="42" ht="62" customHeight="1">
+      <c r="A42" s="16" t="inlineStr">
+        <is>
+          <t>26/08/2026</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Live system research, signed in. Walked the real system and recorded how it actually behaves — the filter panel, the saved-view settings and its three tabs, every field on the RFQ form, the true option values and the page numbering. Written up as a verified reference so later work is checked against fact rather than memory.</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Deliverable: verified reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="62" customHeight="1">
+      <c r="A43" s="16" t="inlineStr">
+        <is>
+          <t>26/08/2026</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Received and catalogued the client's Testing Guideline. Extracted all fifteen sheets into a readable reference and saved both files to the project. This document turns out to be the functional specification, so it now outranks the running system wherever the two disagree.</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Client document</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="62" customHeight="1">
+      <c r="A44" s="16" t="inlineStr">
+        <is>
+          <t>26/08/2026</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Corrections the guideline forced. Required markers changed to red as specified; Historical RFQ restored after being wrongly removed — it appears only when Order Type is Repeat, so it was correctly hidden on the one record checked.</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="62" customHeight="1">
+      <c r="A45" s="16" t="inlineStr">
+        <is>
+          <t>26/08/2026</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Form view completed. Real tab and section names restored, required markers added to nineteen fields, three fields removed that do not exist on the real form, option values corrected and shown as radio choices with their meanings, ITAR built as the access-control rule it actually is, required-field validation added, Quotation Result columns corrected, and the Conversations tab rebuilt with its Comment / Send Email choice and full text editor.</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>6</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Fidelity + build</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="62" customHeight="1">
+      <c r="A46" s="16" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>List view completed. Real columns in the real order, View Detail action restored, page sizes and wording matched, first and last page navigation added, the filter rebuilt as the real one — every field at once, no operators — and saved views built with the View Setting sidebar: choose filter fields, reorder and rename columns, set widths, and stack multiple sort levels.</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Fidelity + build</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="62" customHeight="1">
+      <c r="A47" s="16" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Defects found and fixed while checking. Quoted status badges had been rendering with no colour at all; a column was too narrow for its longest value and made rows uneven; and an empty grid gave the wrong advice, blaming the search when filters were responsible.</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Defect fixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="44" customHeight="1">
+      <c r="A48" s="16" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Client documentation. Prepared the KendoReact licence activation document answering how activation works through npm and what is needed from the client, and this timesheet.</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Deliverable: client document</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C49">
+        <f>SUM(C6:C48)</f>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/docs/Voyager-UIUX-Timesheet-Aug2026.xlsx
+++ b/docs/Voyager-UIUX-Timesheet-Aug2026.xlsx
@@ -545,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -563,7 +563,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Summary by day — for invoicing</t>
+          <t>Summary by day — for invoicing (6 Aug – 6 Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="C5" s="19">
-        <f>SUMIF(Timesheet!$A$6:$A$33,A5,Timesheet!$C$6:$C$33)</f>
+        <f>SUMIF(Timesheet!$A$6:$A$70,A5,Timesheet!$C$6:$C$70)</f>
         <v/>
       </c>
     </row>
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="C6" s="22">
-        <f>SUMIF(Timesheet!$A$6:$A$33,A6,Timesheet!$C$6:$C$33)</f>
+        <f>SUMIF(Timesheet!$A$6:$A$70,A6,Timesheet!$C$6:$C$70)</f>
         <v/>
       </c>
     </row>
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="C7" s="19">
-        <f>SUMIF(Timesheet!$A$6:$A$33,A7,Timesheet!$C$6:$C$33)</f>
+        <f>SUMIF(Timesheet!$A$6:$A$70,A7,Timesheet!$C$6:$C$70)</f>
         <v/>
       </c>
     </row>
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="C8" s="22">
-        <f>SUMIF(Timesheet!$A$6:$A$33,A8,Timesheet!$C$6:$C$33)</f>
+        <f>SUMIF(Timesheet!$A$6:$A$70,A8,Timesheet!$C$6:$C$70)</f>
         <v/>
       </c>
     </row>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="C9" s="19">
-        <f>SUMIF(Timesheet!$A$6:$A$33,A9,Timesheet!$C$6:$C$33)</f>
+        <f>SUMIF(Timesheet!$A$6:$A$70,A9,Timesheet!$C$6:$C$70)</f>
         <v/>
       </c>
     </row>
@@ -676,7 +676,7 @@
         </is>
       </c>
       <c r="C10" s="22">
-        <f>SUMIF(Timesheet!$A$6:$A$33,A10,Timesheet!$C$6:$C$33)</f>
+        <f>SUMIF(Timesheet!$A$6:$A$70,A10,Timesheet!$C$6:$C$70)</f>
         <v/>
       </c>
     </row>
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="C11" s="19">
-        <f>SUMIF(Timesheet!$A$6:$A$33,A11,Timesheet!$C$6:$C$33)</f>
+        <f>SUMIF(Timesheet!$A$6:$A$70,A11,Timesheet!$C$6:$C$70)</f>
         <v/>
       </c>
     </row>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="C12" s="22">
-        <f>SUMIF(Timesheet!$A$6:$A$33,A12,Timesheet!$C$6:$C$33)</f>
+        <f>SUMIF(Timesheet!$A$6:$A$70,A12,Timesheet!$C$6:$C$70)</f>
         <v/>
       </c>
     </row>
@@ -724,40 +724,201 @@
         </is>
       </c>
       <c r="C13" s="19">
-        <f>SUMIF(Timesheet!$A$6:$A$33,A13,Timesheet!$C$6:$C$33)</f>
+        <f>SUMIF(Timesheet!$A$6:$A$70,A13,Timesheet!$C$6:$C$70)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="n"/>
-      <c r="B14" s="13" t="inlineStr">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>26/08/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="18" t="inlineStr">
+        <is>
+          <t>Live system research, Testing Guideline catalogued, form view completed</t>
+        </is>
+      </c>
+      <c r="C14" s="19">
+        <f>SUMIF(Timesheet!$A$6:$A$70,A14,Timesheet!$C$6:$C$70)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="18" t="inlineStr">
+        <is>
+          <t>List view completed, defects fixed, KendoReact licence activation document</t>
+        </is>
+      </c>
+      <c r="C15" s="19">
+        <f>SUMIF(Timesheet!$A$6:$A$70,A15,Timesheet!$C$6:$C$70)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="18" t="inlineStr">
+        <is>
+          <t>Quick Quote and Standard Quote wizards, action bars consolidated</t>
+        </is>
+      </c>
+      <c r="C16" s="19">
+        <f>SUMIF(Timesheet!$A$6:$A$70,A16,Timesheet!$C$6:$C$70)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="18" t="inlineStr">
+        <is>
+          <t>Automated consistency checker, and the first three sweep passes</t>
+        </is>
+      </c>
+      <c r="C17" s="19">
+        <f>SUMIF(Timesheet!$A$6:$A$70,A17,Timesheet!$C$6:$C$70)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t>Resume Draft, Part Master tooling, kick-off deck audit, Login rebuilt</t>
+        </is>
+      </c>
+      <c r="C18" s="19">
+        <f>SUMIF(Timesheet!$A$6:$A$70,A18,Timesheet!$C$6:$C$70)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="18" t="inlineStr">
+        <is>
+          <t>Kendo licence proved, and five screens built: Part Master Detail, BoM, AML, Create Part</t>
+        </is>
+      </c>
+      <c r="C19" s="19">
+        <f>SUMIF(Timesheet!$A$6:$A$70,A19,Timesheet!$C$6:$C$70)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="18" t="inlineStr">
+        <is>
+          <t>Responsive and accessibility checks, open-questions answer sheet</t>
+        </is>
+      </c>
+      <c r="C20" s="19">
+        <f>SUMIF(Timesheet!$A$6:$A$70,A20,Timesheet!$C$6:$C$70)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="18" t="inlineStr">
+        <is>
+          <t>KendoReact migration: grids, export, upload, layering scale, component review</t>
+        </is>
+      </c>
+      <c r="C21" s="19">
+        <f>SUMIF(Timesheet!$A$6:$A$70,A21,Timesheet!$C$6:$C$70)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="17" t="inlineStr">
+        <is>
+          <t>05/09/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="18" t="inlineStr">
+        <is>
+          <t>Dropdowns migrated, tabbed-screen regression fixed, contrast and focus-order sweeps</t>
+        </is>
+      </c>
+      <c r="C22" s="19">
+        <f>SUMIF(Timesheet!$A$6:$A$70,A22,Timesheet!$C$6:$C$70)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="17" t="inlineStr">
+        <is>
+          <t>06/09/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="18" t="inlineStr">
+        <is>
+          <t>Placeholder audit, modal specification, two dialog defects fixed</t>
+        </is>
+      </c>
+      <c r="C23" s="19">
+        <f>SUMIF(Timesheet!$A$6:$A$70,A23,Timesheet!$C$6:$C$70)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="n"/>
+      <c r="B24" s="13" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C14" s="23">
-        <f>SUM(C5:C13)</f>
+      <c r="C24" s="23">
+        <f>SUM(C5:C23)</f>
         <v/>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="24" t="inlineStr">
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="24" t="inlineStr">
         <is>
           <t>This sheet totals the Timesheet tab with SUMIF, so the two cannot disagree. Editing an hour there updates it here.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="24" t="inlineStr">
-        <is>
-          <t>Hours are estimated from scope. Reconcile against your own record before invoicing.</t>
+    <row r="27">
+      <c r="A27" s="24" t="inlineStr">
+        <is>
+          <t>Hours are estimated from scope. Reconcile against your own record before invoicing. The 28 Aug – 6 Sep entries correspond to work packages WP14–WP23 in docs/worklog.md; 26–27 Aug were already logged.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A26:C26"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -769,7 +930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:D80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -795,7 +956,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Work log: 6 August – 25 August 2026</t>
+          <t>Work log: 6 August – 6 September 2026</t>
         </is>
       </c>
     </row>
@@ -1381,220 +1542,817 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="12" t="n"/>
-      <c r="B34" s="13" t="inlineStr">
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>26/08/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Live system research, signed in. Walked the real system and recorded how it actually behaves — the filter panel, the saved-view settings and its three tabs, every field on the RFQ form, the true option values and the page numbering. Written up as a verified reference so later work is checked against fact rather than memory.</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>Deliverable: verified reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>26/08/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>Received and catalogued the client's Testing Guideline. Extracted all fifteen sheets into a readable reference and saved both files to the project. This document turns out to be the functional specification, so it now outranks the running system wherever the two disagree.</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>Client document</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="58" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>26/08/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Corrections the guideline forced. Required markers changed to red as specified; Historical RFQ restored after being wrongly removed — it appears only when Order Type is Repeat, so it was correctly hidden on the one record checked.</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="58" customHeight="1">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>26/08/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>Form view completed. Real tab and section names restored, required markers added to nineteen fields, three fields removed that do not exist on the real form, option values corrected and shown as radio choices with their meanings, ITAR built as the access-control rule it actually is, required-field validation added, Quotation Result columns corrected, and the Conversations tab rebuilt with its Comment / Send Email choice and full text editor.</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="D37" s="11" t="inlineStr">
+        <is>
+          <t>Fidelity + build</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="58" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>List view completed. Real columns in the real order, View Detail action restored, page sizes and wording matched, first and last page navigation added, the filter rebuilt as the real one — every field at once, no operators — and saved views built with the View Setting sidebar: choose filter fields, reorder and rename columns, set widths, and stack multiple sort levels.</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>Fidelity + build</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="58" customHeight="1">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>Defects found and fixed while checking. Quoted status badges had been rendering with no colour at all; a column was too narrow for its longest value and made rows uneven; and an empty grid gave the wrong advice, blaming the search when filters were responsible.</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" s="11" t="inlineStr">
+        <is>
+          <t>Defect fixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="44" customHeight="1">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>Client documentation. Prepared the KendoReact licence activation document answering how activation works through npm and what is needed from the client, and this timesheet.</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>Deliverable: client document</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="44" customHeight="1">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>Quick Quote wizard built out to the guideline's four steps, including the two entry points the sheet describes.</t>
+        </is>
+      </c>
+      <c r="C41" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D41" s="11" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="44" customHeight="1">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>Standard Quote: Load Existing Assembly built as the second entry point into the same wizard.</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="44" customHeight="1">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>Consolidated the screens to one action bar each, removed a duplicated scope control, and applied a single comfortable reading width across the application.</t>
+        </is>
+      </c>
+      <c r="C43" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D43" s="11" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="44" customHeight="1">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>Built an automated consistency checker that reads the stylesheets and reports rules defined twice, classes with no rule behind them, and values that sit outside the design system.</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>Quality: automated check</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="58" customHeight="1">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>Consistency sweep, first three parts: colour contrast, the last remaining browser confirm dialog, and a missing loading state. The finding worth naming is that the application announced failures on the green success message — the words correct and the colour saying the opposite, which is worse than saying nothing.</t>
+        </is>
+      </c>
+      <c r="C45" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D45" s="11" t="inlineStr">
+        <is>
+          <t>Defect fixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="44" customHeight="1">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Consistency sweep, final part: motion added where content is replaced rather than moved, three touch targets brought up to the 24px minimum, and grid links made to fill their cell instead of only their text.</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>Defect fixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="44" customHeight="1">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>Resume Draft Quote built as the third entry point, together with a Save draft that genuinely saves and restores.</t>
+        </is>
+      </c>
+      <c r="C47" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D47" s="11" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="44" customHeight="1">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>Filter, saved views and the column picker wired onto Part Master, so the two list screens now behave identically.</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="58" customHeight="1">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>Checked the kick-off deck against the build for the first time and filed it into the agreed order of precedence. Six of its seven items are covered; the gaps and the two places where it disagrees with later client instructions are recorded so neither is reopened by accident.</t>
+        </is>
+      </c>
+      <c r="C49" s="10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D49" s="11" t="inlineStr">
+        <is>
+          <t>Deliverable: gap analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="44" customHeight="1">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>Login page rebuilt to answer the two faults the deck names by name — too much empty space, and lack of contrast. The width the form must not have now carries the brand instead, and Sign In measures 8.6:1.</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="44" customHeight="1">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="9" t="inlineStr">
+        <is>
+          <t>KendoReact licence key received, recorded with its deployment route, and proved on the deployed prototype with a check page showing a licensed grid rendering without a watermark. Active until 05/06/2029.</t>
+        </is>
+      </c>
+      <c r="C51" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" s="11" t="inlineStr">
+        <is>
+          <t>Setup</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="44" customHeight="1">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>Part Master Detail built as the deck's Data Form View archetype, carrying the Testing Guideline's field list: identity, status chips, reference links, tabs and three-column sections.</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="44" customHeight="1">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="inlineStr">
+        <is>
+          <t>BoM detail and the Where Part Number Used popup, which answers the impact of a shortage or an engineering change.</t>
+        </is>
+      </c>
+      <c r="C53" s="10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D53" s="11" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="44" customHeight="1">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>Bill of Materials list screen, and Create the new BoM across its Config and Review steps.</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="44" customHeight="1">
+      <c r="A55" s="8" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="inlineStr">
+        <is>
+          <t>MFG-MPN (AML), the Approved Manufacturer List, with the stock report and the quantity update the guideline describes.</t>
+        </is>
+      </c>
+      <c r="C55" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D55" s="11" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="44" customHeight="1">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>Create New Part form, and the Import All / Import by Customer choice.</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="58" customHeight="1">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="9" t="inlineStr">
+        <is>
+          <t>Swept the live production system for the components it actually uses, to decide ours against evidence rather than preference — then corrected the sweep after establishing that the method used could not have detected one of them.</t>
+        </is>
+      </c>
+      <c r="C57" s="10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D57" s="11" t="inlineStr">
+        <is>
+          <t>Risk: corrected own finding</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="44" customHeight="1">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>Responsive and accessibility checks across the three packages built that week.</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>Quality / accessibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="44" customHeight="1">
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="9" t="inlineStr">
+        <is>
+          <t>Wrote the open questions up as an answer sheet the client can fill in, ordered so the ones that actually stop work appear first.</t>
+        </is>
+      </c>
+      <c r="C59" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D59" s="11" t="inlineStr">
+        <is>
+          <t>Deliverable: open questions</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="58" customHeight="1">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>Scoped the move to KendoReact before changing anything, then proved the theme on a spike. Scoping first was what established that the work divides into stages that can each be verified, rather than one replacement that cannot be undone.</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="44" customHeight="1">
+      <c r="A61" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="9" t="inlineStr">
+        <is>
+          <t>Migrated the data grids, and with them gained two capabilities that had been written by hand: real Excel export and a real file upload control.</t>
+        </is>
+      </c>
+      <c r="C61" s="10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D61" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="58" customHeight="1">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>Replaced the single layering value every overlay shared with a proper scale. The symptom was an error message rendering behind the Run Quotation dialog and dimmed by its own shading — a message the user could not read telling them what had gone wrong.</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>Defect fixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="58" customHeight="1">
+      <c r="A63" s="8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="9" t="inlineStr">
+        <is>
+          <t>Reviewed the remaining component families one at a time against the live system. Four packages removed, four families moved to Kendo, three deliberately kept with the reason recorded — our undo action is used in 29 places and the Kendo equivalent has nowhere to put it.</t>
+        </is>
+      </c>
+      <c r="C63" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D63" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="58" customHeight="1">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>05/09/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>Dropdowns and the view pickers moved to Kendo. Two data-loss defects were caught in the process: typing over a chosen customer and clicking away silently cleared it, and a committed value could display as blank.</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="58" customHeight="1">
+      <c r="A65" s="8" t="inlineStr">
+        <is>
+          <t>05/09/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="9" t="inlineStr">
+        <is>
+          <t>Fixed a layout regression the migration introduced on every tabbed screen, where a three-column form collapsed into one narrow column. Reported by the client. Then measured all six tabbed screens rather than assuming the fix reached them.</t>
+        </is>
+      </c>
+      <c r="C65" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D65" s="11" t="inlineStr">
+        <is>
+          <t>Defect fixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="58" customHeight="1">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>05/09/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>Colour contrast swept across the application with a measuring harness that was first proved able to detect a planted failure, so its clean results could be trusted. Text passes everywhere; three control borders failed and were corrected by one new token.</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>Quality / accessibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="58" customHeight="1">
+      <c r="A67" s="8" t="inlineStr">
+        <is>
+          <t>05/09/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="9" t="inlineStr">
+        <is>
+          <t>Keyboard focus order and row density swept across the record, wizard, result and checklist screens. Two questions raised for the client rather than guessed at: which four fields are switches, and whether error messages may name fields the user cannot see.</t>
+        </is>
+      </c>
+      <c r="C67" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D67" s="11" t="inlineStr">
+        <is>
+          <t>Quality / accessibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="58" customHeight="1">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>06/09/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>Audited all nineteen 'not in this prototype' placeholders against what has since been built. Six turned out to be missing wiring rather than a missing feature — five of them the buttons at the top of the RFQ record, whose destinations sit on the same page. Now connected.</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="58" customHeight="1">
+      <c r="A69" s="8" t="inlineStr">
+        <is>
+          <t>06/09/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="9" t="inlineStr">
+        <is>
+          <t>Wrote the modal specification. Modal behaviour is defined in no client document — the Testing Guideline names around 25 of them and their contents but never how one should behave, and the kick-off deck's six archetypes are all full-page screens. The eight rules the prototype's 22 dialogs already follow are now written down for the client to review as a set.</t>
+        </is>
+      </c>
+      <c r="C69" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D69" s="11" t="inlineStr">
+        <is>
+          <t>Deliverable: modal specification</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="58" customHeight="1">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>06/09/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>Fixed two defects found while writing that specification. One press of Escape closed every open dialog rather than the innermost, and Escape with a dropdown open dismissed the dropdown and the form behind it, losing the entry. Verified across nine dialogs and three levels of nesting.</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>Defect fixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="12" t="n"/>
+      <c r="B71" s="13" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C34" s="14">
-        <f>SUM(C6:C33)</f>
+      <c r="C71" s="14">
+        <f>SUM(C6:C70)</f>
         <v/>
       </c>
-      <c r="D34" s="12" t="n"/>
-    </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" s="15" t="inlineStr">
+      <c r="D71" s="12" t="n"/>
+    </row>
+    <row r="72"/>
+    <row r="73">
+      <c r="A73" s="15" t="inlineStr">
         <is>
           <t>Notes on this log</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="16" t="inlineStr">
-        <is>
-          <t>•  Entries for 06/08 and 10/08 were supplied by the consultant; all other entries are reconstructed from the project's version-control history, which records 44 commits across 19–25 August.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="30" customHeight="1">
-      <c r="A38" s="16" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="16" t="inlineStr">
+        <is>
+          <t>•  Entries for 06/08 and 10/08 were supplied by the consultant; all other entries are reconstructed from the project's version-control history, which records 152 commits across 19 August – 6 September.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="16" t="inlineStr">
         <is>
           <t>•  Hours are an estimate of the effort each task represents. Version control records when work was committed, not how long it took, so these figures should be reconciled against the consultant's own record before invoicing.</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="30" customHeight="1">
-      <c r="A39" s="16" t="inlineStr">
-        <is>
-          <t>•  Three entries are marked as risk avoided rather than features delivered. The metadata verification (24/08) caught option lists that would have caused the built system to reject valid user input. The bundle forensics (24/08) recovered specifications for features that would otherwise have been rebuilt from guesswork. The requirements decisions (24/08) avoid a change-management cost across 51 screens and every current user.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="30" customHeight="1">
-      <c r="A40" s="16" t="inlineStr">
-        <is>
-          <t>•  The prototype does not use a commercial component library, as no licence is available for this project. All functional requirements are met using licence-free components; the only cost is implementation time.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="30" customHeight="1">
-      <c r="A41" s="16" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="16" t="inlineStr">
+        <is>
+          <t>•  Three entries are marked as risk avoided rather than features delivered. The metadata verification (24/08) caught option lists that would have caused the built system to reject valid user input. The bundle forensics (24/08) recovered specifications for features that would otherwise have been rebuilt from guesswork. The requirements decisions (24/08) avoid a change-management cost across 51 screens and every current user. Two later entries carry the same mark: the export-control field (27/08), which was rendering as a label instead of restricting access, and the component sweep of 31/08, corrected after its own method proved unable to detect one of the components it reported on.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="16" t="inlineStr">
+        <is>
+          <t>•  The prototype now uses KendoReact. The line this replaces said the opposite, and was true when written: no licence existed. The key arrived on 31/08, and the client then chose Kendo so the mockup would not look unlike the system their staff already use. Three component families were deliberately not migrated, each for a stated reason.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="16" t="inlineStr">
         <is>
           <t>•  Current phase covers layout and user experience. Visual design — colour, spacing, typography and component styling — is a later phase, so that it is not done twice.</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="62" customHeight="1">
-      <c r="A42" s="16" t="inlineStr">
-        <is>
-          <t>26/08/2026</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Live system research, signed in. Walked the real system and recorded how it actually behaves — the filter panel, the saved-view settings and its three tabs, every field on the RFQ form, the true option values and the page numbering. Written up as a verified reference so later work is checked against fact rather than memory.</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Deliverable: verified reference</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="62" customHeight="1">
-      <c r="A43" s="16" t="inlineStr">
-        <is>
-          <t>26/08/2026</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Received and catalogued the client's Testing Guideline. Extracted all fifteen sheets into a readable reference and saved both files to the project. This document turns out to be the functional specification, so it now outranks the running system wherever the two disagree.</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Client document</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="62" customHeight="1">
-      <c r="A44" s="16" t="inlineStr">
-        <is>
-          <t>26/08/2026</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Corrections the guideline forced. Required markers changed to red as specified; Historical RFQ restored after being wrongly removed — it appears only when Order Type is Repeat, so it was correctly hidden on the one record checked.</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>1</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Correction</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="62" customHeight="1">
-      <c r="A45" s="16" t="inlineStr">
-        <is>
-          <t>26/08/2026</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Form view completed. Real tab and section names restored, required markers added to nineteen fields, three fields removed that do not exist on the real form, option values corrected and shown as radio choices with their meanings, ITAR built as the access-control rule it actually is, required-field validation added, Quotation Result columns corrected, and the Conversations tab rebuilt with its Comment / Send Email choice and full text editor.</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>6</v>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Fidelity + build</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="62" customHeight="1">
-      <c r="A46" s="16" t="inlineStr">
-        <is>
-          <t>27/08/2026</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>List view completed. Real columns in the real order, View Detail action restored, page sizes and wording matched, first and last page navigation added, the filter rebuilt as the real one — every field at once, no operators — and saved views built with the View Setting sidebar: choose filter fields, reorder and rename columns, set widths, and stack multiple sort levels.</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Fidelity + build</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="62" customHeight="1">
-      <c r="A47" s="16" t="inlineStr">
-        <is>
-          <t>27/08/2026</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Defects found and fixed while checking. Quoted status badges had been rendering with no colour at all; a column was too narrow for its longest value and made rows uneven; and an empty grid gave the wrong advice, blaming the search when filters were responsible.</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>1</v>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Defect fixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="44" customHeight="1">
-      <c r="A48" s="16" t="inlineStr">
-        <is>
-          <t>27/08/2026</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Client documentation. Prepared the KendoReact licence activation document answering how activation works through npm and what is needed from the client, and this timesheet.</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>1</v>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Deliverable: client document</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C49">
-        <f>SUM(C6:C48)</f>
-        <v/>
+    <row r="80">
+      <c r="A80" s="16" t="inlineStr">
+        <is>
+          <t>•  Correction, 07/09: the 26/08 and 27/08 entries had been appended BELOW this notes block and were excluded from the total and from the Summary tab, understating the log by 19.5 hours. They are now in the table above, unchanged, and both totals cover every row.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="A37:D37"/>
-    <mergeCell ref="A38:D38"/>
-    <mergeCell ref="A39:D39"/>
-    <mergeCell ref="A41:D41"/>
+  <mergeCells count="6">
+    <mergeCell ref="A80:D80"/>
+    <mergeCell ref="A75:D75"/>
+    <mergeCell ref="A77:D77"/>
+    <mergeCell ref="A74:D74"/>
+    <mergeCell ref="A78:D78"/>
+    <mergeCell ref="A76:D76"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
